--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Device.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="390">
   <si>
     <t>Property</t>
   </si>
@@ -436,6 +436,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -475,6 +485,10 @@
     <t>The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>.id</t>
   </si>
   <si>
@@ -497,6 +511,16 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -572,6 +596,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -604,6 +631,9 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -736,6 +766,9 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -743,6 +776,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -998,6 +1034,9 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1047,6 +1086,16 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1113,6 +1162,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1164,6 +1217,9 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1540,14 +1596,14 @@
     <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="52.640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="230.36328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -2519,19 +2575,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2543,7 +2599,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>128</v>
@@ -2557,10 +2613,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2586,16 +2642,16 @@
         <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>134</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2632,19 +2688,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2656,7 +2712,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>128</v>
@@ -2670,10 +2726,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2696,16 +2752,16 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2755,7 +2811,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2764,27 +2820,27 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2807,15 +2863,17 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2864,22 +2922,22 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AG12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>77</v>
@@ -2890,10 +2948,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2916,16 +2974,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2975,7 +3033,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2984,16 +3042,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3001,10 +3059,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3027,13 +3085,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3084,7 +3142,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3099,7 +3157,7 @@
         <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
@@ -3110,10 +3168,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3142,7 +3200,7 @@
         <v>132</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>134</v>
@@ -3183,19 +3241,19 @@
         <v>77</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3207,10 +3265,10 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
@@ -3221,14 +3279,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3250,16 +3308,16 @@
         <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>134</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3308,7 +3366,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3320,7 +3378,7 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>128</v>
@@ -3334,14 +3392,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3360,15 +3418,17 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3417,7 +3477,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3432,25 +3492,25 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3472,12 +3532,14 @@
         <v>99</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3526,7 +3588,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3541,21 +3603,21 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3581,14 +3643,16 @@
         <v>99</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3637,7 +3701,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3652,7 +3716,7 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3663,14 +3727,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3689,16 +3753,16 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3748,7 +3812,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3763,25 +3827,25 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3800,16 +3864,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3859,7 +3923,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3874,21 +3938,21 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3914,14 +3978,14 @@
         <v>105</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3946,13 +4010,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -3970,7 +4034,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3985,7 +4049,7 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
@@ -3996,10 +4060,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4025,13 +4089,13 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4057,13 +4121,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4081,7 +4145,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4096,10 +4160,10 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4107,10 +4171,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4133,15 +4197,17 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4166,13 +4232,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4190,7 +4256,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4199,16 +4265,16 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4216,14 +4282,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4242,16 +4308,16 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4301,7 +4367,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4316,21 +4382,21 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4353,15 +4419,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4410,7 +4478,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4425,10 +4493,10 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>128</v>
@@ -4436,10 +4504,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4462,13 +4530,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4519,7 +4587,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4534,21 +4602,21 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4571,13 +4639,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4628,7 +4696,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4643,21 +4711,21 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4680,15 +4748,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4737,7 +4807,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4752,21 +4822,21 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4789,16 +4859,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4848,7 +4918,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4863,10 +4933,10 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4874,10 +4944,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4900,13 +4970,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4957,7 +5027,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4966,13 +5036,13 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -4983,10 +5053,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5009,13 +5079,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5066,7 +5136,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5081,7 +5151,7 @@
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
@@ -5092,10 +5162,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5124,7 +5194,7 @@
         <v>132</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>134</v>
@@ -5165,19 +5235,19 @@
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5189,10 +5259,10 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
@@ -5203,14 +5273,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5232,16 +5302,16 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>134</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5290,7 +5360,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5302,7 +5372,7 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>128</v>
@@ -5316,14 +5386,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5342,15 +5412,17 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5399,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -5425,10 +5497,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5454,10 +5526,10 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5484,13 +5556,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5508,7 +5580,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>85</v>
@@ -5523,10 +5595,10 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5534,10 +5606,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5560,15 +5632,17 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5617,7 +5691,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5632,10 +5706,10 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5643,10 +5717,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5669,16 +5743,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5728,7 +5802,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5743,10 +5817,10 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5754,10 +5828,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5780,15 +5854,17 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5813,13 +5889,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5837,7 +5913,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5846,13 +5922,13 @@
         <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5863,10 +5939,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5889,13 +5965,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5946,7 +6022,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5955,13 +6031,13 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -5972,10 +6048,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5998,13 +6074,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6055,7 +6131,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6070,7 +6146,7 @@
         <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -6081,10 +6157,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6113,7 +6189,7 @@
         <v>132</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>134</v>
@@ -6154,19 +6230,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6178,10 +6254,10 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6192,14 +6268,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6221,16 +6297,16 @@
         <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>134</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6279,7 +6355,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6291,7 +6367,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>128</v>
@@ -6305,14 +6381,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6331,15 +6407,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6388,7 +6466,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6397,13 +6475,13 @@
         <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
@@ -6414,10 +6492,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6440,15 +6518,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6497,7 +6577,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6515,7 +6595,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6523,10 +6603,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6549,13 +6629,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6606,7 +6686,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6615,13 +6695,13 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
@@ -6632,10 +6712,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6658,13 +6738,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6715,7 +6795,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6730,7 +6810,7 @@
         <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -6741,10 +6821,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6773,7 +6853,7 @@
         <v>132</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>134</v>
@@ -6814,19 +6894,19 @@
         <v>77</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6838,10 +6918,10 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
@@ -6852,14 +6932,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6881,16 +6961,16 @@
         <v>131</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>134</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -6939,7 +7019,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6951,7 +7031,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>128</v>
@@ -6965,14 +7045,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6991,15 +7071,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7048,7 +7130,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7057,13 +7139,13 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
@@ -7074,10 +7156,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7100,13 +7182,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7157,7 +7239,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7166,16 +7248,16 @@
         <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7183,10 +7265,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7209,15 +7291,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7266,7 +7350,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7292,10 +7376,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7318,13 +7402,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7375,7 +7459,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7384,13 +7468,13 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
@@ -7401,10 +7485,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7427,13 +7511,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7484,7 +7568,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7499,7 +7583,7 @@
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
@@ -7510,10 +7594,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7542,7 +7626,7 @@
         <v>132</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>134</v>
@@ -7583,19 +7667,19 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7607,10 +7691,10 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7621,14 +7705,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7650,16 +7734,16 @@
         <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>134</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7708,7 +7792,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7720,7 +7804,7 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>128</v>
@@ -7734,10 +7818,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7760,15 +7844,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -7817,7 +7903,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>85</v>
@@ -7826,13 +7912,13 @@
         <v>85</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -7843,10 +7929,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7869,15 +7955,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -7926,7 +8014,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7935,13 +8023,13 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>340</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -7952,10 +8040,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7978,15 +8066,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8035,7 +8125,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8044,13 +8134,13 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>77</v>
@@ -8061,10 +8151,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8087,17 +8177,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8146,7 +8238,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8155,16 +8247,16 @@
         <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8172,10 +8264,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8198,15 +8290,17 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8255,7 +8349,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8264,16 +8358,16 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8281,10 +8375,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8307,16 +8401,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8366,7 +8460,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8375,16 +8469,16 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8392,10 +8486,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8418,17 +8512,19 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8477,7 +8573,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8486,16 +8582,16 @@
         <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8503,10 +8599,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8532,13 +8628,13 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8588,7 +8684,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8603,10 +8699,10 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8614,10 +8710,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8640,15 +8736,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8697,7 +8795,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8706,13 +8804,13 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>77</v>
@@ -8723,10 +8821,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8749,15 +8847,17 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8806,7 +8906,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -8815,13 +8915,13 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
@@ -8832,10 +8932,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8858,15 +8958,17 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -8915,7 +9017,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -8924,13 +9026,13 @@
         <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>77</v>

--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Device.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Device.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
